--- a/AAII_Financials/Quarterly/LBTYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LBTYA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>LBTYA</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1920500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1854500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1848000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1868400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1841900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1746300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1754200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1853300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1920800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1901400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2989200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3499900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3311700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2845400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5388300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2875800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2982200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2840900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2850400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2868000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2860200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2929700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3015600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3063500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2902700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2929000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2774900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3519000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4216600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4313100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>951300</v>
+      </c>
+      <c r="E9" s="3">
         <v>887900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>880300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>872300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>856100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>759900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>747900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>810000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>830900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>801900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1281300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1588100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1484200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1247200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2308500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1275200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1254600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1201500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1204100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1219800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1155400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1214500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1229800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1310100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1180800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1229300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1113600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1332100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1533800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1561300</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>969200</v>
+      </c>
+      <c r="E10" s="3">
         <v>966600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>967700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>996100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>985800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>986400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1006300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1043300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1089900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1099500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1707900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1911800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1827500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1598200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3079800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1600600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1727600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1639400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1646300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1648200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1704800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1715200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1785800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1753400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1721900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1699700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1661300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2186900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2682800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2751800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,192 +1298,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-391500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-637800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-184300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>150800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-11040600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>44400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>76500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>448900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>85500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>135300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>84500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>55800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>70900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>63800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>135000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>50000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>63300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>134900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>91900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>66700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>57100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>229200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>89800</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>633400</v>
+      </c>
+      <c r="E15" s="3">
         <v>584000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>570900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>526900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>583000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>506000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>517700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>564700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>608900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>582300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>555300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>607200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>517100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>432000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1278100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>783500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>897900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>892900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>921800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>939600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>905400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>929400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>964000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1040700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1047200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>953700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>922000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1128300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1187500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1216200</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2127200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1504100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1897200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1831000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1887200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1630300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1033600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1794500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1743000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1934000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-8595400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2898700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2699700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2201900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4846100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2649700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2819100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2680600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2724300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2762500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2628600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2752200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2771600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2945900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2873300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2744700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2619600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3137200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3681500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3614000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-206700</v>
+      </c>
+      <c r="E18" s="3">
         <v>350400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-49200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>37400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-45300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>116000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>720600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>58800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>177800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-32600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11584600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>601200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>612000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>643500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>542200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>226100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>163100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>160300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>126100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>105500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>231600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>177500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>244000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>117600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>29400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>184300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>155300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>381800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>535100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>699100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3033500</v>
+      </c>
+      <c r="E20" s="3">
         <v>712000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-94500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-537500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4357200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2530200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1758100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1232300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>623600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>491300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>115600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1321400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1345300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1515300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>448700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1185000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-928700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>696200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-75300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-17300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>482800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>67400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>712600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-399500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-296200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-324400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-499100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-82700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>922800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-229700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2606800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1646400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>427200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3819500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3152200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2996400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1855800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1410300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>988800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12280700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2556800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-189700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-413300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2320100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2194600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>132300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1749400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>972600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1027800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1619800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1180200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1920600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>758800</v>
       </c>
-      <c r="AA21" s="3" t="s">
+      <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2603300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1445900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1427400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2645400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1685600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>251900</v>
+      </c>
+      <c r="E22" s="3">
         <v>241400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>208400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>172500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>149700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>132900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>134200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>134000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>140900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>272500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>334700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>313300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>279300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>594200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>313300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>314900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>340100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>363600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>367300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>358100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>363000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>380400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>375300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>367800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>360000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>348800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>453200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>609100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>569300</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3492100</v>
+      </c>
+      <c r="E23" s="3">
         <v>821000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-352100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-701000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4575000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2496500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2345800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1156900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>667400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>317800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11427700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1587900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1046600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1151100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>396700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1097800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1080500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>516400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-312800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-279100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>356300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-118100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>576200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-657200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-634600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-500100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-692600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-154100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>848800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-99900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>159200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>109300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>64800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>63600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>81200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>29100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>276800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>165200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-23700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-165500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-86700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>80100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>269200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-70800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>26800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>27800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>678800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>108600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>149200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-500500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>26700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>61800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>68700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>102200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1392500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3471700</v>
+      </c>
+      <c r="E26" s="3">
         <v>822700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-511300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-713500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4684300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2431700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2282200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1075700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>638300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>315600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11150900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1422700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1022900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-985600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>483400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1017700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1349700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>587200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-339600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-306900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-322500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-226700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>427000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-156700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-661300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-561900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-761300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-256300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2241300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-136800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3489900</v>
+      </c>
+      <c r="E27" s="3">
         <v>659200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-499600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-721400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4697200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2348000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1937700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1003700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>597800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>274000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11104600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1367800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1046400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1035100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>395100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>949800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1391100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>550000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-369100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-315600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-349600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-278500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>389100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-164600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-631300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-574500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-783200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-309300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2235200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2558,85 +2618,88 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-2500</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>848900</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>34600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>38300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>3100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>64800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>17600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>15900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>12000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>30500</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>4600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>12297900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>422100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>322600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>374700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>1252600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>991700</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-1023700</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1215800</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-217100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>108900</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-10900</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3033500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-712000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>94500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>537500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4357200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2530200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1758100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1232300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-623600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-491300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-115600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1321400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1345300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1515300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-448700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1185000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>928700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-696200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>75300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>17300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-482800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-67400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-712600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>399500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>296200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>324400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>499100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>82700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-922800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>229700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3489900</v>
+      </c>
+      <c r="E33" s="3">
         <v>659200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-499600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-721400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4699700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2348000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2786600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1038300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>636100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>277100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11169400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1385400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1030500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1023100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>425600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>949800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1386500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12847900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>53000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>25100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>974100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1380800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1188300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1847100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-791600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-674300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-320200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2235200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3489900</v>
+      </c>
+      <c r="E35" s="3">
         <v>659200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-499600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-721400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4699700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2348000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2786600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1038300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>636100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>277100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11169400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1385400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1030500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1023100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>425600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>949800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1386500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12847900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>53000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>25100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>974100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1380800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1188300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1847100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-791600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-674300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-320200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2235200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,150 +3437,154 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1415900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1741600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1565200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1446200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1726200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1594100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2391100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>843400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>910600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>766200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>874300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>928700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1327200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3777200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4360600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5440500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8142400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7382000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1269000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>939400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1480500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>949200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>862400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>554900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1672400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1579100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1090700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2109600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1076600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>506100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1990500</v>
+      </c>
+      <c r="E42" s="3">
         <v>1557000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2126000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2187900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2621600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2149000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1527000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1958200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2269600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2511400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2866000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1571700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1600200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2549300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2650800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1640200</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>8</v>
@@ -3512,8 +3601,8 @@
       <c r="X42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3536,100 +3625,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>870100</v>
+      </c>
+      <c r="E43" s="3">
         <v>825100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>872200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>830600</v>
       </c>
       <c r="G43" s="3">
         <v>830600</v>
       </c>
       <c r="H43" s="3">
+        <v>830600</v>
+      </c>
+      <c r="I43" s="3">
         <v>726400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>767600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>876000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>907300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>943100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>927200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>860000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1078400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>519300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>498400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1250200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1404800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1221100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1298400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1258900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1342100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1300200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1323600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1623600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1404500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1399300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1333400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1272800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3721500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1220400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,468 +3815,486 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1365100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1304300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1379800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1195200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1119000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1001000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>918800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1966500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1853000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1740800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>833400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>756100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1796600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>909700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1130000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1432000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1026100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1189600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1504000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1478900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1318800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1325700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1385500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1279300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1653100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>901400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1579100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>886100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>765900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>841800</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5641600</v>
+      </c>
+      <c r="E46" s="3">
         <v>5428000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5943200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5659900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6297400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5470500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5604500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5644100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5940500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5961500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5500900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4116500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5802400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7755500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8639800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9762900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10573300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9792700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4071400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3677200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4141400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3575100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3571500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3457800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4331600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3879800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4003200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4268500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5564000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2568300</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13396100</v>
+      </c>
+      <c r="E47" s="3">
         <v>15186900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>16236800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16384700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14856100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16432200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>17715200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19160300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>19703000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19549200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20220900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5425000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5354500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5005300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4731400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4567600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4782000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4728000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4945000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5014400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5121800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5522300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6317800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6862200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6671400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6709100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6582600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6518600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6388700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2149900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9122000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8660700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8346400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8406600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8228900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7601100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8058300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7891600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8309300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8300000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8946900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8890500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9066900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6618600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6510400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13615400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14356100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13550400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14139700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14329800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13878900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14047600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14053000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20196300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14149000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>19498400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>18717900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17471000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17249300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17786400</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12530600</v>
+      </c>
+      <c r="E49" s="3">
         <v>11786100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11773500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11696700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11658500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10886800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11015000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11570700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11865900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11820500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12612400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12524200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12845600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6973500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6760600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13914200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14624200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13939600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>14551100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>14643500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>14747000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>15152900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>15329700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>20888300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15962600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>21149400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>20796500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>19620600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>19486900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>20815900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1397600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1634700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1636600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1657900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1854100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2227800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1766600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1280800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1098300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1213600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1273500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26491200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26588400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24810500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>20698000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5395900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4710700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6167900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16279800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15772700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>15264500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15422300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16438900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6907000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>17669500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5530400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5573700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5667700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5829000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>23569500</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42087900</v>
+      </c>
+      <c r="E54" s="3">
         <v>42696400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43936500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43805800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>42895000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42618400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44159600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>45547500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>46917000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46844800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>48554600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57447400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>59092700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>51163400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>47340200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47256000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>49046300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>48178600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>53987000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>53437600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>53153600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>53720200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>55710900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>58311600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57596800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>56767100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>55673900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>53546400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>54517900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>66890000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>689800</v>
+      </c>
+      <c r="E57" s="3">
         <v>585800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>616200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>478500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>610100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>502600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>513400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>567300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>613400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>529900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>599200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>616300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>579100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>450100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>410000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>723300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>963900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>818200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>771900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>761000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>874300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>811100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>831000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1061200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>926000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1009500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1056200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>981000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>954500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>806800</v>
+      </c>
+      <c r="E58" s="3">
         <v>633300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>704100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>758500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>799700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>716700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>764800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>815300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>850300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>986500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>982100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1059000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2216500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1832700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1867700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3942800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3877200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3380500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3680500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3679400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3615200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3499400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3392600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4290700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3667500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4014600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3550600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2822400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2624300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1996700</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2836200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2511700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2767800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2468000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2511200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2165700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2308100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2570600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2621100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2542300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2610800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2472500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4627100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1956600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2072000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3493900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3810600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3549100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5880800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5734800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5816600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5722500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5761300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5036900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6438300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4576300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4561900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4155600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4818500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4560300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4332800</v>
+      </c>
+      <c r="E60" s="3">
         <v>3730800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4088100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3705000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3921000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3385000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3586300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3953200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4084800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4058700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4192100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4147800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4511100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4239400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4349700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8160000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8651700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7747800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10333200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10175200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10306100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10033000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9984900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10388800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9965800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9600400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9168700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7959000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8397300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7408000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14959100</v>
+      </c>
+      <c r="E61" s="3">
         <v>14558300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14405700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14289200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12963500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12503200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12483600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13781300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13974800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14097300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14274600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13245400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13861300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10166000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10375900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23455700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>24305300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24096200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>26235600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>26360300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26190000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26232000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28425900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>38276000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28977000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>37643000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>36937200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35421700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34886500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35947900</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3788600</v>
+      </c>
+      <c r="E62" s="3">
         <v>3559700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3502000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3442100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3437100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3241100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3284100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2805900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3259400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3096100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3537900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26566100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>30417300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23993000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20064100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2728100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2890700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2973000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13747500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13052500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12509200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12639800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12548200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4012100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12338800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2633200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2432500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2157900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2235500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16347100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23025300</v>
+      </c>
+      <c r="E66" s="3">
         <v>21775100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22080300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21583400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20458600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19241700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19383600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20279700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20982100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20936800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21672500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>43651400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45430100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38067700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34406200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>34011900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>35440100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34391300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>49853500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>49077500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>48472200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48313300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>50592700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>52279000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>50791800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>49436600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>48074300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>45068700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>45009200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>59189900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,85 +6200,88 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15566000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19055900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18396700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18896300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19617700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24317400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21969400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19182800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18144500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17508400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17205700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6077500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4692100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5722600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6745700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7269900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6350400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7736900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5111000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5164000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5172200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5197300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6171400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-7084000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6217600</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>8</v>
@@ -6122,8 +6295,11 @@
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19062600</v>
+      </c>
+      <c r="E76" s="3">
         <v>20921300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21856200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22222400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22436400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23376700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24776000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25267800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25934900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25908000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26882100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13796000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13662600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13095700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12934000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13244100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13606200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13787300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4133500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4360100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4681400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5406900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5118200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6032600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6805000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7330500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7599600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8477700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9508700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7700100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3489900</v>
+      </c>
+      <c r="E81" s="3">
         <v>659200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-499600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-721400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4699700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2348000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2786600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1038300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>636100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>277100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11169400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1385400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1030500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1023100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>425600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>949800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1386500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12847900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>53000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>25100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>974100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1380800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1188300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1847100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-791600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-674300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-320200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2235200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>633400</v>
+      </c>
+      <c r="E83" s="3">
         <v>584000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>570900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>526900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>583000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>506000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>517700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>564700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>608900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>530100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>580500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>634200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>543600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>458500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1329200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>783500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>897900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>892900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>921800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>939600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>905400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>935300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>721100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1296400</v>
       </c>
-      <c r="AA83" s="3" t="s">
+      <c r="AB83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3523300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2306800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1128300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1187500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1216200</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>839200</v>
+      </c>
+      <c r="E89" s="3">
         <v>327100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>691800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>307800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>883200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>540500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>757400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>656700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>991300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>612600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1123900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>821200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1493500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1100400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1591900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>449800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1493900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>633800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1692300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>765400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1762700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>935300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1985800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1279300</v>
       </c>
-      <c r="AA89" s="3" t="s">
+      <c r="AB89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4043600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2653600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>997400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1653300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1253200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-369800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-327800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-311200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-377200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-373900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-295100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-261400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-372800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-293600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-245500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-393100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-475800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-389700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-310900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-649600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-347800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-343000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-267200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-301600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-331300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-310100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-345100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-310600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-484200</v>
       </c>
-      <c r="AA91" s="3" t="s">
+      <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-850700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-588000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1000800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-809500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-249900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-878600</v>
+      </c>
+      <c r="E94" s="3">
         <v>519900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-63100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1423200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-651200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-633500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2620700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-55000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-308900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4924000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-509400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4701500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-538100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3634400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2349200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-268300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>10436300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-416100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-477300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-320300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1584900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-506200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-671100</v>
       </c>
-      <c r="AA94" s="3" t="s">
+      <c r="AB94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>507000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>964700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1890700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-641900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-430400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-349300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-638100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-518800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>813800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-213400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-628000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1776300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-658300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-784300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-399400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>337500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-699700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>735400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2069500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1721300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-783200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-487500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4925300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-948000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-815800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-893400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2414200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1149800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1732400</v>
       </c>
-      <c r="AA100" s="3" t="s">
+      <c r="AB100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3701500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1748600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-419600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1105600</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-32200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>22000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>113600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-76000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-54800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-12300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>60800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-46300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>120800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>30600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-10400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-16200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>33000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-28800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-7600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-11400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-23400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>14100</v>
       </c>
-      <c r="AA101" s="3" t="s">
+      <c r="AB101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>108200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>93700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>22600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-21300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-325600</v>
+      </c>
+      <c r="E102" s="3">
         <v>176700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>119000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-279600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>132200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-797000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1547000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-67100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>144000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-108000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3401800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-434200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2351800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2662400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3774200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2698800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>771100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6116000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>330800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-535300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>537600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>81600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>307100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1110100</v>
       </c>
-      <c r="AA102" s="3" t="s">
+      <c r="AB102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>503000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>699700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1033200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>570500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-279600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LBTYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LBTYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>LBTYA</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1945100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1920500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1854500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1848000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1868400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1841900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1746300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1754200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1853300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1920800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1901400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2989200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3499900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3311700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2845400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5388300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2875800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2982200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2840900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2850400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2868000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2860200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2929700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3015600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3063500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2902700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2929000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2774900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3519000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4216600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4313100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>980700</v>
+      </c>
+      <c r="E9" s="3">
         <v>951300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>887900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>880300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>872300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>856100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>759900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>747900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>810000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>830900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>801900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1281300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1588100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1484200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1247200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2308500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1275200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1254600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1201500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1204100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1219800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1155400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1214500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1229800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1310100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1180800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1229300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1113600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1332100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1533800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1561300</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>964400</v>
+      </c>
+      <c r="E10" s="3">
         <v>969200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>966600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>967700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>996100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>985800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>986400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1006300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1043300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1089900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1099500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1707900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1911800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1827500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1598200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3079800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1600600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1727600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1639400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1646300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1648200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1704800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1715200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1785800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1753400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1721900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1699700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1661300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2186900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2682800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2751800</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,198 +1318,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E14" s="3">
         <v>62700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-391500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-637800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-184300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>150800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-11040600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>44400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>76500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-16100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>448900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>85500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>135300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>84500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>55800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>70900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>63800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>135000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>50000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>63300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>134900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>91900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>66700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>57100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>229200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>89800</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>480700</v>
+      </c>
+      <c r="E15" s="3">
         <v>633400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>584000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>570900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>526900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>583000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>506000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>517700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>564700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>608900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>582300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>555300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>607200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>517100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>432000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1278100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>783500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>897900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>892900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>921800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>939600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>905400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>929400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>964000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1040700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1047200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>953700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>922000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1128300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1187500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>1216200</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1922500</v>
+      </c>
+      <c r="E17" s="3">
         <v>2127200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1504100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1897200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1831000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1887200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1630300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1033600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1794500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1743000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1934000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-8595400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2898700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2699700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2201900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4846100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2649700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2819100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2680600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2724300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2762500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2628600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2752200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2771600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2945900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2873300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2744700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2619600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3137200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3681500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3614000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-206700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>350400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-49200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-45300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>116000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>720600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>58800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>177800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-32600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11584600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>601200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>612000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>643500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>542200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>226100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>163100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>160300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>126100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>105500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>231600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>177500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>244000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>117600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>29400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>184300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>155300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>381800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>535100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>699100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>784800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3033500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>712000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-94500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-537500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4357200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2530200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1758100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1232300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>623600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>491300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>115600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1321400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1345300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1515300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>448700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1185000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-928700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>696200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-75300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-17300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>482800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>67400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>712600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-399500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-296200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-324400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-499100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-82700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>922800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-229700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1288100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2606800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1646400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>427200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>26800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3819500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3152200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2996400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1855800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1410300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>988800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12280700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2556800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-189700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-413300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2320100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2194600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>132300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1749400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>972600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1027800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1619800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1180200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1920600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>758800</v>
       </c>
-      <c r="AB21" s="3" t="s">
+      <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2603300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1445900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1427400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2645400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1685600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>253500</v>
+      </c>
+      <c r="E22" s="3">
         <v>251900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>241400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>208400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>172500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>149700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>132900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>134200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>134000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>140900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>272500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>334700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>313300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>279300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>594200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>313300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>314900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>340100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>363600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>367300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>358100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>363000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>380400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>375300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>367800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>360000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>348800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>453200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>609100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>569300</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>553900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3492100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>821000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-352100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-701000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4575000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2496500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2345800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1156900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>667400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>317800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11427700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1587900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1046600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1151100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>396700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1097800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1080500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>516400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-312800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-279100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>356300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-118100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>576200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-657200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-634600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-500100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-692600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-154100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>848800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-99900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-20400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>159200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>109300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>63600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>81200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>276800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>165200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-165500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-86700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>80100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>269200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-70800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>26800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>27800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>678800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>108600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>149200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-500500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>26700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>61800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>68700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>102200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1392500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>527000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3471700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>822700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-511300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-713500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4684300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2431700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2282200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1075700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>638300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>315600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11150900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1422700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1022900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-985600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>483400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1017700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1349700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>587200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-339600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-306900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-322500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-226700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>427000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-156700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-661300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-561900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-761300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-256300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2241300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-136800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>510000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3489900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>659200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-499600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-721400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4697200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2348000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1937700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1003700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>597800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>274000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11104600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1367800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1046400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1035100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>395100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>949800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1391100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>550000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-369100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-315600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-349600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-278500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>389100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-164600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-631300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-574500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-783200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-309300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2235200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,13 +2661,16 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2621,85 +2682,88 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-2500</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>848900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>34600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>38300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>3100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>64800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>17600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>15900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>12000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>30500</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>4600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>12297900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>422100</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>322600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>374700</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>1252600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>991700</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1023700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-1215800</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-217100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>108900</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-10900</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-784800</v>
+      </c>
+      <c r="E32" s="3">
         <v>3033500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-712000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>94500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>537500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4357200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2530200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1758100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1232300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-623600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-491300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-115600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1321400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1345300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1515300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-448700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1185000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>928700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-696200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>75300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>17300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-482800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-67400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-712600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>399500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>296200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>324400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>499100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>82700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-922800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>229700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>510000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3489900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>659200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-499600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-721400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4699700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2348000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2786600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1038300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>636100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>277100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11169400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1385400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1030500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1023100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>425600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>949800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1386500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12847900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>53000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>25100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>974100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1380800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1188300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1847100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-791600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-674300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-320200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2235200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>510000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3489900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>659200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-499600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-721400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4699700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2348000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2786600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1038300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>636100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>277100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11169400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1385400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1030500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1023100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>425600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>949800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1386500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12847900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>53000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>25100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>974100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1380800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1188300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1847100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-791600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-674300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-320200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2235200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,156 +3524,160 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1139600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1415900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1741600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1565200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1446200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1726200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1594100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2391100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>843400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>910600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>766200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>874300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>928700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1327200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3777200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4360600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5440500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8142400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7382000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1269000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>939400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1480500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>949200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>862400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>554900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1672400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1579100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1090700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2109600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1076600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>506100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1652800</v>
+      </c>
+      <c r="E42" s="3">
         <v>1990500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1557000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2126000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2187900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2621600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2149000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1527000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1958200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2269600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2511400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2866000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1571700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1600200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2549300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2650800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1640200</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>8</v>
@@ -3604,8 +3694,8 @@
       <c r="Y42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3628,103 +3718,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>858600</v>
+      </c>
+      <c r="E43" s="3">
         <v>870100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>825100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>872200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>830600</v>
       </c>
       <c r="H43" s="3">
         <v>830600</v>
       </c>
       <c r="I43" s="3">
+        <v>830600</v>
+      </c>
+      <c r="J43" s="3">
         <v>726400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>767600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>876000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>907300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>943100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>927200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>860000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1078400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>519300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>498400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1250200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1404800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1221100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1298400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1258900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1342100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1300200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1323600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1623600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1404500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1399300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1333400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1272800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3721500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1220400</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,483 +3914,501 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1218400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1365100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1304300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1379800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1195200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1119000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1001000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>918800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1966500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1853000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1740800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>833400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>756100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1796600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>909700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1130000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1432000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1026100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1189600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1504000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1478900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1318800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1325700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1385500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1279300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1653100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>901400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1579100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>886100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>765900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>841800</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4869400</v>
+      </c>
+      <c r="E46" s="3">
         <v>5641600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5428000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5943200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5659900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6297400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5470500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5604500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5644100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5940500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5961500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5500900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4116500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5802400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7755500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8639800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9762900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10573300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9792700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4071400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3677200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4141400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3575100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3571500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3457800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4331600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3879800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4003200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4268500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5564000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2568300</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13462300</v>
+      </c>
+      <c r="E47" s="3">
         <v>13396100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15186900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16236800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16384700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14856100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16432200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>17715200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>19160300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19703000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>19549200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20220900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5425000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5354500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5005300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4731400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4567600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4782000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4728000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4945000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5014400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5121800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5522300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6317800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6862200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6671400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6709100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6582600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6518600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6388700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2149900</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9273900</v>
+      </c>
+      <c r="E48" s="3">
         <v>9122000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8660700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8346400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8406600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8228900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7601100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8058300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7891600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8309300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8300000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8946900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8890500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9066900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6618600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6510400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13615400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14356100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13550400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14139700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14329800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13878900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14047600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14053000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20196300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>14149000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19498400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18717900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17471000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17249300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17786400</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11738100</v>
+      </c>
+      <c r="E49" s="3">
         <v>12530600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11786100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11773500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11696700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11658500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10886800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11015000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11570700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11865900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11820500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12612400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12524200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12845600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6973500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6760600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13914200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14624200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>13939600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>14551100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>14643500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>14747000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>15152900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15329700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>20888300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>15962600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>21149400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>20796500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>19620600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>19486900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>20815900</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1216000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1397600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1634700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1636600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1657900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1854100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2227800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1766600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1280800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1098300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1213600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1273500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26491200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26588400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>24810500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>20698000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5395900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4710700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6167900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16279800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>15772700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15264500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>15422300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16438900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6907000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>17669500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5530400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5573700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5667700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5829000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>23569500</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40559700</v>
+      </c>
+      <c r="E54" s="3">
         <v>42087900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42696400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43936500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43805800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42895000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42618400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44159600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>45547500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46917000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46844800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>48554600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57447400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>59092700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>51163400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47340200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47256000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>49046300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>48178600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>53987000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>53437600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>53153600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>53720200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>55710900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>58311600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>57596800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>56767100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>55673900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>53546400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>54517900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>66890000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>537300</v>
+      </c>
+      <c r="E57" s="3">
         <v>689800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>585800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>616200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>478500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>610100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>502600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>513400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>567300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>613400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>529900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>599200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>616300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>579100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>450100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>410000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>723300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>963900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>818200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>771900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>761000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>874300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>811100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>831000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1061200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>926000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1009500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1056200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>981000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>954500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>737800</v>
+      </c>
+      <c r="E58" s="3">
         <v>806800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>633300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>704100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>758500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>799700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>716700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>764800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>815300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>850300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>986500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>982100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1059000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2216500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1832700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1867700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3942800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3877200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3380500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3680500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3679400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3615200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3499400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3392600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4290700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3667500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4014600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3550600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2822400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2624300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1996700</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2528800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2836200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2511700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2767800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2468000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2511200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2165700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2308100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2570600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2621100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2542300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2610800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2472500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4627100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1956600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2072000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3493900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3810600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3549100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5880800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5734800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5816600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5722500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5761300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5036900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6438300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4576300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4561900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4155600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4818500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4560300</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3803900</v>
+      </c>
+      <c r="E60" s="3">
         <v>4332800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3730800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4088100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3705000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3921000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3385000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3586300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3953200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4084800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4058700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4192100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4147800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4511100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4239400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4349700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8160000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8651700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7747800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10333200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10175200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10306100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10033000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9984900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10388800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9965800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9600400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9168700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7959000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8397300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7408000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14782600</v>
+      </c>
+      <c r="E61" s="3">
         <v>14959100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14558300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14405700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14289200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12963500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12503200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12483600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13781300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13974800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14097300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14274600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13245400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13861300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10166000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10375900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23455700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24305300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24096200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>26235600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26360300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26190000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>26232000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28425900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>38276000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28977000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37643000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>36937200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35421700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34886500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35947900</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3581800</v>
+      </c>
+      <c r="E62" s="3">
         <v>3788600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3559700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3502000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3442100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3437100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3241100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3284100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2805900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3259400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3096100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3537900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26566100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>30417300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23993000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20064100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2728100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2890700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2973000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13747500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13052500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12509200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12639800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>12548200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4012100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12338800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2633200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2432500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2157900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2235500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>16347100</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22130600</v>
+      </c>
+      <c r="E66" s="3">
         <v>23025300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21775100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22080300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21583400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20458600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19241700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19383600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20279700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20982100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20936800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21672500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43651400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45430100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38067700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>34406200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34011900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>35440100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34391300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>49853500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>49077500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48472200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48313300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>50592700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>52279000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>50791800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>49436600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>48074300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>45068700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>45009200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>59189900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,88 +6374,91 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16076000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15566000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19055900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18396700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18896300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19617700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>24317400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21969400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19182800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18144500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17508400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17205700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6077500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4692100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5722600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6745700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7269900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6350400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7736900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5111000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5164000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5172200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5197300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-6171400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-7084000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-6217600</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
@@ -6298,8 +6472,11 @@
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18429100</v>
+      </c>
+      <c r="E76" s="3">
         <v>19062600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20921300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21856200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22222400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22436400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23376700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24776000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25267800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25934900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25908000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26882100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13796000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13662600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13095700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12934000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13244100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13606200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13787300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4133500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4360100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4681400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5406900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5118200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6032600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6805000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7330500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7599600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8477700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9508700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7700100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>510000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3489900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>659200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-499600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-721400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4699700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2348000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2786600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1038300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>636100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>277100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11169400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1385400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1030500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1023100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>425600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>949800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1386500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12847900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>53000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>25100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>974100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1380800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1188300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1847100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-791600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-674300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-320200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2235200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>480700</v>
+      </c>
+      <c r="E83" s="3">
         <v>633400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>584000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>570900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>526900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>583000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>506000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>517700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>564700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>608900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>530100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>580500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>634200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>543600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>458500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1329200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>783500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>897900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>892900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>921800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>939600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>905400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>935300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>721100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1296400</v>
       </c>
-      <c r="AB83" s="3" t="s">
+      <c r="AC83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3523300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2306800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1128300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1187500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1216200</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>245700</v>
+      </c>
+      <c r="E89" s="3">
         <v>839200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>327100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>691800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>307800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>883200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>540500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>757400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>656700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>991300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>612600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1123900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>821200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1493500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1100400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1591900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>449800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1493900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>633800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1692300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>765400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1762700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>935300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1985800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1279300</v>
       </c>
-      <c r="AB89" s="3" t="s">
+      <c r="AC89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4043600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2653600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>997400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1653300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1253200</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-350800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-369800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-327800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-311200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-377200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-373900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-295100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-261400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-372800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-293600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-245500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-393100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-475800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-389700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-310900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-649600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-347800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-343000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-267200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-301600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-331300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-310100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-345100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-310600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-484200</v>
       </c>
-      <c r="AB91" s="3" t="s">
+      <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-850700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-588000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1000800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-809500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-249900</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-211700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-878600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>519900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-63100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1423200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-651200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-633500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2620700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-55000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-54200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-308900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4924000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-509400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4701500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-538100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3634400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2349200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-268300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>10436300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-416100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-477300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-320300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1584900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-506200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-671100</v>
       </c>
-      <c r="AB94" s="3" t="s">
+      <c r="AC94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>507000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>964700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1890700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-641900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-430400</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-349300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-638100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-518800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>813800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-213400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-628000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1776300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-658300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-784300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-399400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>337500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-699700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>735400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2069500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1721300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-783200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-487500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4925300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-948000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-815800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-893400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2414200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1149800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1732400</v>
       </c>
-      <c r="AB100" s="3" t="s">
+      <c r="AC100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3701500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1748600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-419600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1105600</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E101" s="3">
         <v>63100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-32200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>22000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>113600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-76000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-54800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-10500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-12300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>60800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-46300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>120800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>30600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-10400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-16200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>33000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-28800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-7600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-23400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>14100</v>
       </c>
-      <c r="AB101" s="3" t="s">
+      <c r="AC101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>108200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>93700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>22600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-21300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-275600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-325600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>176700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>119000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-279600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>132200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-797000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1547000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-67100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>144000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-108000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3401800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-434200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2351800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2662400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3774200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2698800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>771100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6116000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>330800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-535300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>537600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>81600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>307100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1110100</v>
       </c>
-      <c r="AB102" s="3" t="s">
+      <c r="AC102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>503000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>699700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1033200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>570500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-279600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LBTYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LBTYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>LBTYA</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1873700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1945100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1920500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1854500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1848000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1868400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1841900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1746300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1754200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1853300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1920800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1901400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2989200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3499900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3311700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2845400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5388300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2875800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2982200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2840900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2850400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2868000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2860200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2929700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3015600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3063500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2902700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2929000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2774900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3519000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4216600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4313100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>881700</v>
+      </c>
+      <c r="E9" s="3">
         <v>980700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>951300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>887900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>880300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>872300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>856100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>759900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>747900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>810000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>830900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>801900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1281300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1588100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1484200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1247200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2308500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1275200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1254600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1201500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1204100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1219800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1155400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1214500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1229800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1310100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1180800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1229300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1113600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1332100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1533800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1561300</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>992000</v>
+      </c>
+      <c r="E10" s="3">
         <v>964400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>969200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>966600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>967700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>996100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>985800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>986400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1006300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1043300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1089900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1099500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1707900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1911800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1827500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1598200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3079800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1600600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1727600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1639400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1646300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1648200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1704800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1715200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1785800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1753400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1721900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1699700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1661300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2186900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2682800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2751800</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,204 +1338,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E14" s="3">
         <v>33500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>62700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-391500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>16400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-637800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-184300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>150800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-11040600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>44400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>76500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-16100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>448900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>85500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>135300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>84500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>55800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>70900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>63800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>135000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>50000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>63300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>134900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>91900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>66700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>57100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>229200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>89800</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>531400</v>
+      </c>
+      <c r="E15" s="3">
         <v>480700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>633400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>584000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>570900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>526900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>583000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>506000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>517700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>564700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>608900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>582300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>555300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>607200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>517100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>432000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1278100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>783500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>897900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>892900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>921800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>939600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>905400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>929400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>964000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1040700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1047200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>953700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>922000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1128300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>1187500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>1216200</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1854600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1922500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2127200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1504100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1897200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1831000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1887200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1630300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1033600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1794500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1743000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1934000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-8595400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2898700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2699700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2201900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4846100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2649700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2819100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2680600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2724300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2762500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2628600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2752200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2771600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2945900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2873300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2744700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2619600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3137200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3681500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3614000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E18" s="3">
         <v>22600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-206700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>350400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-49200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>37400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-45300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>116000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>720600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>58800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>177800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11584600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>601200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>612000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>643500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>542200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>226100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>163100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>160300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>126100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>105500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>231600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>177500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>244000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>117600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>29400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>184300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>155300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>381800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>535100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>699100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>568300</v>
+      </c>
+      <c r="E20" s="3">
         <v>784800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3033500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>712000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-94500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-537500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4357200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2530200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1758100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1232300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>623600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>491300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>115600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1321400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1345300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1515300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>448700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1185000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-928700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>696200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-75300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-17300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>482800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>67400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>712600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-399500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-296200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-324400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-499100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-82700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>922800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-229700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1118800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1288100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2606800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1646400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>427200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>26800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3819500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3152200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2996400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1855800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1410300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>988800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12280700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2556800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-189700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-413300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2320100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2194600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>132300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1749400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>972600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1027800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1619800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1180200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1920600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>758800</v>
       </c>
-      <c r="AC21" s="3" t="s">
+      <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2603300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1445900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1427400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2645400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1685600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>251500</v>
+      </c>
+      <c r="E22" s="3">
         <v>253500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>251900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>241400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>208400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>200900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>172500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>149700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>132900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>134200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>134000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>140900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>272500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>334700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>313300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>279300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>594200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>313300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>314900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>340100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>363600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>367300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>358100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>363000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>380400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>375300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>367800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>360000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>348800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>453200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>609100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>569300</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>335900</v>
+      </c>
+      <c r="E23" s="3">
         <v>553900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3492100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>821000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-352100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-701000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4575000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2496500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2345800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1156900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>667400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>317800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11427700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1587900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1046600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1151100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>396700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1097800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1080500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>516400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-312800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-279100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>356300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-118100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>576200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-657200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-634600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-500100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-692600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-154100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>848800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-99900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E24" s="3">
         <v>26900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-20400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>159200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>109300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>64800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>63600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>81200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>276800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>165200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-23700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-165500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-86700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>80100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>269200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-70800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>26800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>27800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>678800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>108600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>149200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-500500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>26700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>61800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>68700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>102200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-1392500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>275200</v>
+      </c>
+      <c r="E26" s="3">
         <v>527000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3471700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>822700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-511300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-713500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4684300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2431700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2282200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1075700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>638300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>315600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11150900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1422700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1022900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-985600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>483400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1017700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1349700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>587200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-339600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-306900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-322500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-226700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>427000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-156700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-661300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-561900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-761300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-256300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2241300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-136800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>268100</v>
+      </c>
+      <c r="E27" s="3">
         <v>510000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3489900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>659200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-499600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-721400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4697200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2348000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1937700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1003700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>597800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>274000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11104600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1367800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1046400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1035100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>395100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>949800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1391100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>550000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-369100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-315600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-349600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-278500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>389100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-164600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-631300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-574500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-783200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-309300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2235200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,16 +2722,19 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2685,85 +2746,88 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2500</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>848900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>34600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>38300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>3100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>64800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>17600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>15900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>12000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>30500</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>4600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>12297900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>422100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>322600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>374700</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>1252600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>991700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-1023700</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-1215800</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-217100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>108900</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-10900</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-568300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-784800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3033500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-712000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>94500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>537500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4357200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2530200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1758100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1232300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-623600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-491300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-115600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1321400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1345300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1515300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-448700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1185000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>928700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-696200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>75300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>17300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-482800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-67400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-712600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>399500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>296200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>324400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>499100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>82700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-922800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>229700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>268100</v>
+      </c>
+      <c r="E33" s="3">
         <v>510000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3489900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>659200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-499600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-721400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4699700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2348000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2786600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1038300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>636100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>277100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11169400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1385400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1030500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1023100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>425600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>949800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1386500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>12847900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>53000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>25100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>974100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1380800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1188300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1847100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-791600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-674300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-320200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2235200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>268100</v>
+      </c>
+      <c r="E35" s="3">
         <v>510000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3489900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>659200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-499600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-721400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4699700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2348000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2786600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1038300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>636100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>277100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11169400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1385400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1030500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1023100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>425600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>949800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1386500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>12847900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>53000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>25100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>974100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1380800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1188300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1847100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-791600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-674300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-320200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2235200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,162 +3611,166 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2011300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1139600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1415900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1741600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1565200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1446200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1726200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1594100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2391100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>843400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>910600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>766200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>874300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>928700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1327200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3777200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4360600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5440500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8142400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7382000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1269000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>939400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1480500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>949200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>862400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>554900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1672400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1579100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1090700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2109600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1076600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>506100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1204500</v>
+      </c>
+      <c r="E42" s="3">
         <v>1652800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1990500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1557000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2126000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2187900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2621600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2149000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1527000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1958200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2269600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2511400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2866000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1571700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1600200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2549300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2650800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1640200</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>8</v>
@@ -3697,8 +3787,8 @@
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>858800</v>
+      </c>
+      <c r="E43" s="3">
         <v>858600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>870100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>825100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>872200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>830600</v>
       </c>
       <c r="I43" s="3">
         <v>830600</v>
       </c>
       <c r="J43" s="3">
+        <v>830600</v>
+      </c>
+      <c r="K43" s="3">
         <v>726400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>767600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>876000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>907300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>943100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>927200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>860000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1078400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>519300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>498400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1250200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1404800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1221100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1298400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1258900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1342100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1300200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1323600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1623600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1404500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1399300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1333400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1272800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3721500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1220400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,498 +4013,516 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1313000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1218400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1365100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1304300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1379800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1195200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1119000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1001000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>918800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1966500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1853000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1740800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>833400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>756100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1796600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>909700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1130000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1432000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1026100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1189600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1504000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1478900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1318800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1325700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1385500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1279300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1653100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>901400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1579100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>886100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>765900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>841800</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5387600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4869400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5641600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5428000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5943200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5659900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6297400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5470500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5604500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5644100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5940500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5961500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5500900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4116500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5802400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7755500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8639800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9762900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10573300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9792700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4071400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3677200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4141400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3575100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3571500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3457800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4331600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3879800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4003200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4268500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5564000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2568300</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13260000</v>
+      </c>
+      <c r="E47" s="3">
         <v>13462300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>13396100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15186900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16236800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16384700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14856100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>16432200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>17715200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19160300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>19703000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>19549200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20220900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5425000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5354500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>5005300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4731400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4567600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4782000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4728000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4945000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5014400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5121800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5522300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6317800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6862200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6671400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6709100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6582600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6518600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6388700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2149900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9299800</v>
+      </c>
+      <c r="E48" s="3">
         <v>9273900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9122000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8660700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8346400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8406600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8228900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7601100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8058300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7891600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8309300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8300000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8946900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8890500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9066900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6618600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6510400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13615400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14356100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13550400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14139700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14329800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13878900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14047600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14053000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20196300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14149000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19498400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18717900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17471000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>17249300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>17786400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11567700</v>
+      </c>
+      <c r="E49" s="3">
         <v>11738100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12530600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11786100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11773500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11696700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11658500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10886800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11015000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11570700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11865900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11820500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12612400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12524200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12845600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6973500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6760600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13914200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>14624200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>13939600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>14551100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>14643500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>14747000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15152900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15329700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>20888300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>15962600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>21149400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>20796500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>19620600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>19486900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>20815900</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1323200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1216000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1397600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1634700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1636600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1657900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1854100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2227800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1766600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1280800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1098300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1213600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1273500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26491200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26588400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>24810500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>20698000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5395900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4710700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6167900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16279800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15772700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>15264500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>15422300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16438900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6907000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17669500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5530400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5573700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5667700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5829000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>23569500</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40838300</v>
+      </c>
+      <c r="E54" s="3">
         <v>40559700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>42087900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42696400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43936500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43805800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42895000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42618400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44159600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45547500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46917000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>46844800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>48554600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57447400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>59092700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>51163400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47340200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47256000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>49046300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>48178600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>53987000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>53437600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>53153600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>53720200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>55710900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>58311600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>57596800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>56767100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>55673900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>53546400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>54517900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>66890000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>514900</v>
+      </c>
+      <c r="E57" s="3">
         <v>537300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>689800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>585800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>616200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>478500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>610100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>502600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>513400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>567300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>613400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>529900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>599200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>616300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>579100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>450100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>410000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>723300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>963900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>818200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>771900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>761000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>874300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>811100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>831000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1061200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>926000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1009500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1056200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>981000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>954500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>771400</v>
+      </c>
+      <c r="E58" s="3">
         <v>737800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>806800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>633300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>704100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>758500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>799700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>716700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>764800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>815300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>850300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>986500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>982100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1059000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2216500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1832700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1867700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3942800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3877200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3380500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3680500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3679400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3615200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3499400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3392600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4290700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3667500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4014600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3550600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2822400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2624300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1996700</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2744100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2528800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2836200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2511700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2767800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2468000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2511200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2165700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2308100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2570600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2621100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2542300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2610800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2472500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4627100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1956600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2072000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3493900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3810600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3549100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5880800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5734800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5816600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5722500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5761300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5036900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6438300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4576300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4561900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4155600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4818500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4560300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4030400</v>
+      </c>
+      <c r="E60" s="3">
         <v>3803900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4332800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3730800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4088100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3705000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3921000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3385000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3586300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3953200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4084800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4058700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4192100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4147800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4511100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4239400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4349700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8160000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8651700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7747800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10333200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10175200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10306100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10033000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9984900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10388800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9965800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9600400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9168700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7959000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8397300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7408000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14740800</v>
+      </c>
+      <c r="E61" s="3">
         <v>14782600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14959100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14558300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14405700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14289200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12963500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12503200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12483600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13781300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13974800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14097300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14274600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13245400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13861300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10166000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10375900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23455700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24305300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>24096200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26235600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26360300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>26190000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>26232000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28425900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>38276000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28977000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37643000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>36937200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35421700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>34886500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>35947900</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3750300</v>
+      </c>
+      <c r="E62" s="3">
         <v>3581800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3788600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3559700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3502000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3442100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3437100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3241100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3284100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2805900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3259400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3096100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3537900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26566100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30417300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23993000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20064100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2728100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2890700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2973000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13747500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13052500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12509200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>12639800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12548200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4012100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>12338800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2633200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2432500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2157900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2235500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>16347100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22490800</v>
+      </c>
+      <c r="E66" s="3">
         <v>22130600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23025300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21775100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22080300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21583400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20458600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19241700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19383600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20279700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20982100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20936800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21672500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>43651400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45430100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38067700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34406200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34011900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35440100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34391300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>49853500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>49077500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48472200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>48313300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>50592700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>52279000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>50791800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>49436600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>48074300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>45068700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>45009200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>59189900</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,91 +6548,94 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16344100</v>
+      </c>
+      <c r="E72" s="3">
         <v>16076000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15566000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19055900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18396700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18896300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19617700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24317400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21969400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19182800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18144500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17508400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17205700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6077500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4692100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5722600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6745700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7269900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6350400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7736900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5111000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5164000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5172200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5197300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6171400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-7084000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-6217600</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE72" s="3" t="s">
         <v>8</v>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18347500</v>
+      </c>
+      <c r="E76" s="3">
         <v>18429100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19062600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20921300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21856200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22222400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22436400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23376700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24776000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25267800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25934900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25908000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26882100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13796000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13662600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13095700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12934000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13244100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13606200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13787300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4133500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4360100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4681400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5406900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5118200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6032600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6805000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7330500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7599600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8477700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9508700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7700100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>268100</v>
+      </c>
+      <c r="E81" s="3">
         <v>510000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3489900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>659200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-499600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-721400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4699700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2348000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2786600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1038300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>636100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>277100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11169400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1385400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1030500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1023100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>425600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>949800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1386500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>12847900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>53000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>25100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>974100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1380800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1188300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1847100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-791600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-674300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-320200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2235200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-167700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>531400</v>
+      </c>
+      <c r="E83" s="3">
         <v>480700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>633400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>584000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>570900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>526900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>583000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>506000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>517700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>564700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>608900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>530100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>580500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>634200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>543600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>458500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1329200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>783500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>897900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>892900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>921800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>939600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>905400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>935300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>721100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1296400</v>
       </c>
-      <c r="AC83" s="3" t="s">
+      <c r="AD83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3523300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2306800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1128300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1187500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1216200</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>546100</v>
+      </c>
+      <c r="E89" s="3">
         <v>245700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>839200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>327100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>691800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>307800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>883200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>540500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>757400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>656700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>991300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>612600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1123900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>821200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1493500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1100400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1591900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>449800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1493900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>633800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1692300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>765400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1762700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>935300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1985800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1279300</v>
       </c>
-      <c r="AC89" s="3" t="s">
+      <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4043600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2653600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>997400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1653300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1253200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-289300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-350800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-369800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-327800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-311200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-377200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-373900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-295100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-261400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-372800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-293600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-245500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-393100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-475800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-389700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-310900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-649600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-347800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-343000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-267200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-301600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-331300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-310100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-345100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-310600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-484200</v>
       </c>
-      <c r="AC91" s="3" t="s">
+      <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-850700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-588000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1000800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-809500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-249900</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>522400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-211700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-878600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>519900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-63100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1423200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-651200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-633500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2620700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-55000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-308900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4924000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-509400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4701500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-538100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3634400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2349200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-268300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>10436300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-416100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-477300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-320300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1584900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-506200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-671100</v>
       </c>
-      <c r="AC94" s="3" t="s">
+      <c r="AD94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>507000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>964700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1890700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-641900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-430400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-189300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-284000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-349300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-638100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-518800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>813800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-213400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-628000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1776300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-658300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-784300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-399400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>337500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-699700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>735400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2069500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1721300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-783200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-487500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4925300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-948000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-815800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-893400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2414200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1149800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1732400</v>
       </c>
-      <c r="AC100" s="3" t="s">
+      <c r="AD100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3701500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1748600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-419600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1105600</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-25600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>63100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-32200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>22000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>113600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-76000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-54800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-10500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-12300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>60800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-46300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>120800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>30600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-10400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-16200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>33000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-28800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-23400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>14100</v>
       </c>
-      <c r="AC101" s="3" t="s">
+      <c r="AD101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>108200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>93700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>22600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-21300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>871800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-275600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-325600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>176700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>119000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-279600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>132200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-797000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1547000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>144000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-108000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3401800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-434200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2351800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2662400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3774200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2698800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>771100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6116000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>330800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-535300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>537600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>81600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>307100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1110100</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AD102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>503000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>699700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1033200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>570500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-279600</v>
       </c>
     </row>
